--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux. Maman dit : le jeu est fini. On va ranger. Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine. Maman dit : merci. Plus tard, Kenzo joue aux voitures dans le couloir. Les roues font un bruit léger. Maman dit : on range. Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
+          <t>Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux. Le jeu est fini. On va ranger. Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine. Merci. Plus tard, Kenzo joue aux voitures dans le couloir. Les roues font un bruit léger. On range. Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux.
+maman|Le jeu est fini. On va ranger.
+narrateur|Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine.
+maman|Merci. Plus tard, Kenzo joue aux voitures dans le couloir.
+narrateur|Les roues font un bruit léger.
+maman|On range.
+narrateur|Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu est fini. Que fait Kenzo ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a rangé les cubes. Puis les voitures. Dans la caisse, deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La caisse est fermée. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le jeu est fini. Que fait Kenzo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Kenzo a rangé les cubes. Puis les voitures. Dans la caisse, deux fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|La caisse est fermée. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo range dans la caisse, deux fois</t>
+          <t>La caisse d'Amir, deux fois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir range les cubes dans la caisse. Plus tard, dans le couloir, il range aussi les voitures. Même leçon, autre lieu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux. Le jeu est fini. On va ranger. Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine. Merci. Plus tard, Kenzo joue aux voitures dans le couloir. Les roues font un bruit léger. On range. Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
+          <t>Dans la maison, l'horloge fait tic-tac. Une odeur de pain chaud vient de la cuisine. Le couloir est long, un peu frais. Le tapis du salon est épais et doux. Le pain est sorti, maman. Merci, papa. Il sent bon. Et maintenant, Amir est au salon. Des cubes attendent dans une caisse en bois. Amir les sort, un par un. Les cubes font un bruit sec. Je fais une maison, maman. Une maison en cubes. Elle est solide ? Oui. Elle est solide. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Ta maison a une porte ? Une petite porte, papa. Puis le jeu est fini. Le jeu est fini, Amir. On va ranger. Les jouets retournent dans la caisse. Amir prend les cubes, un par un. Il les met dans la caisse. Toc. Toc. Toc. Bravo. Ranger, c'est mettre dans la caisse. La caisse se remplit. Le tapis redevient vide. Tu as fini de ranger tes jouets ? Oui, papa. Les cubes sont dans la caisse. Merci, Amir. Tu as fait du bon travail. Plus tard, le couloir est calme. Amir sort de petites voitures. Les roues font un bruit léger. Elles vont jusqu'à la porte. Elles roulent bien. Puis ce jeu se termine aussi. On range. Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Même leçon, autre lieu. Parce que tu ranges, le couloir est libre. Amir a rangé deux fois. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux.
-maman|Le jeu est fini. On va ranger.
-narrateur|Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine.
-maman|Merci. Plus tard, Kenzo joue aux voitures dans le couloir.
+          <t>narrateur|Dans la maison, l'horloge fait tic-tac.
+narrateur|Une odeur de pain chaud vient de la cuisine.
+narrateur|Le couloir est long, un peu frais.
+narrateur|Le tapis du salon est épais et doux.
+papa|Le pain est sorti, maman.
+maman|Merci, papa. Il sent bon.
+narrateur|Et maintenant, Amir est au salon.
+narrateur|Des cubes attendent dans une caisse en bois.
+narrateur|Amir les sort, un par un.
+narrateur|Les cubes font un bruit sec.
+enfant-m|Je fais une maison, maman.
+maman|Une maison en cubes. Elle est solide ?
+enfant-m|Oui. Elle est solide.
+narrateur|Amir pose un cube rouge.
+narrateur|Puis un cube bleu.
+narrateur|La maison grandit au milieu du tapis.
+papa|Ta maison a une porte ?
+enfant-m|Une petite porte, papa.
+narrateur|Puis le jeu est fini.
+maman|Le jeu est fini, Amir.
+maman|On va ranger.
+maman|Les jouets retournent dans la caisse.
+narrateur|Amir prend les cubes, un par un.
+narrateur|Il les met dans la caisse.
+narrateur|Toc. Toc. Toc.
+maman|Bravo. Ranger, c'est mettre dans la caisse.
+narrateur|La caisse se remplit.
+narrateur|Le tapis redevient vide.
+papa|Tu as fini de ranger tes jouets ?
+enfant-m|Oui, papa. Les cubes sont dans la caisse.
+maman|Merci, Amir. Tu as fait du bon travail.
+narrateur|Plus tard, le couloir est calme.
+narrateur|Amir sort de petites voitures.
 narrateur|Les roues font un bruit léger.
+enfant-m|Elles vont jusqu'à la porte.
+papa|Elles roulent bien.
+narrateur|Puis ce jeu se termine aussi.
 maman|On range.
-narrateur|Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.</t>
+narrateur|Amir se souvient.
+narrateur|Il prend les voitures.
+narrateur|Il les met dans la caisse.
+enfant-m|Dans la caisse, comme les cubes.
+maman|Oui. Même leçon, autre lieu.
+papa|Parce que tu ranges, le couloir est libre.
+narrateur|Amir a rangé deux fois.
+maman|Bravo, Amir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Kenzo ?</t>
+          <t>Le jeu est fini. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1553,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le jeu est fini. Que fait Kenzo ?</t>
+          <t>narrateur|Le jeu est fini. Que fait Amir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a rangé les cubes. Puis les voitures. Dans la caisse, deux fois.</t>
+          <t>Amir a rangé les cubes. Puis les voitures. Dans la caisse, deux fois. Tu t'es souvenu, Amir. Les jouets vont dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Le salon est calme. Le couloir est libre. Tu as fini de ranger tes jouets ? Oui. Deux fois. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1725,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a rangé les cubes. Puis les voitures. Dans la caisse, deux fois.</t>
+          <t>narrateur|Amir a rangé les cubes.
+narrateur|Puis les voitures.
+narrateur|Dans la caisse, deux fois.
+maman|Tu t'es souvenu, Amir.
+enfant-m|Les jouets vont dans la caisse.
+papa|Oui. Ranger, c'est mettre dans la caisse.
+maman|Le salon est calme.
+maman|Le couloir est libre.
+papa|Tu as fini de ranger tes jouets ?
+enfant-m|Oui. Deux fois.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La caisse est fermée. Maman sourit.</t>
+          <t>La caisse est fermée. Ça fait toc. L'horloge fait encore tic-tac. Tu veux une petite tranche de pain ? Oui, papa. Papa lui tend un morceau encore un peu chaud. On s'assoit un moment ? Amir s'assoit près de maman. Le tapis est doux sous les pieds. La caisse est pleine. Oui. Merci, Amir. Bravo. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1903,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La caisse est fermée. Maman sourit.</t>
+          <t>narrateur|La caisse est fermée.
+narrateur|Ça fait toc.
+narrateur|L'horloge fait encore tic-tac.
+papa|Tu veux une petite tranche de pain ?
+enfant-m|Oui, papa.
+narrateur|Papa lui tend un morceau encore un peu chaud.
+maman|On s'assoit un moment ?
+narrateur|Amir s'assoit près de maman.
+narrateur|Le tapis est doux sous les pieds.
+enfant-m|La caisse est pleine.
+maman|Oui. Merci, Amir.
+papa|Bravo. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai rangé deux fois, dans la caisse. Bravo. Les cubes et les voitures sont rentrés. L'odeur du pain reste un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2082,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai rangé deux fois, dans la caisse.
+maman|Bravo.
+papa|Les cubes et les voitures sont rentrés.
+narrateur|L'odeur du pain reste un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La caisse d'Amir, deux fois</t>
+          <t>Le pain d'Amir</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir range les cubes dans la caisse. Plus tard, dans le couloir, il range aussi les voitures. Même leçon, autre lieu.</t>
+          <t>Amir veut livrer le pain chaud jusqu'au bout du couloir. Les cubes gênent les voitures. Il range deux fois. Ils goûtent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dans la maison, l'horloge fait tic-tac. Une odeur de pain chaud vient de la cuisine. Le couloir est long, un peu frais. Le tapis du salon est épais et doux. Le pain est sorti, maman. Merci, papa. Il sent bon. Et maintenant, Amir est au salon. Des cubes attendent dans une caisse en bois. Amir les sort, un par un. Les cubes font un bruit sec. Je fais une maison, maman. Une maison en cubes. Elle est solide ? Oui. Elle est solide. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Ta maison a une porte ? Une petite porte, papa. Puis le jeu est fini. Le jeu est fini, Amir. On va ranger. Les jouets retournent dans la caisse. Amir prend les cubes, un par un. Il les met dans la caisse. Toc. Toc. Toc. Bravo. Ranger, c'est mettre dans la caisse. La caisse se remplit. Le tapis redevient vide. Tu as fini de ranger tes jouets ? Oui, papa. Les cubes sont dans la caisse. Merci, Amir. Tu as fait du bon travail. Plus tard, le couloir est calme. Amir sort de petites voitures. Les roues font un bruit léger. Elles vont jusqu'à la porte. Elles roulent bien. Puis ce jeu se termine aussi. On range. Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Même leçon, autre lieu. Parce que tu ranges, le couloir est libre. Amir a rangé deux fois. Bravo, Amir.</t>
+          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui. Il craque. Le couloir est un peu frais. Le tapis du salon est épais. Amir est à genoux au milieu. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui. Avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Les voitures vont chercher le pain. Jusqu'au bout du couloir. Oui. On le mange là-bas. Papa pose un petit morceau de pain près de la porte. Il est encore tiède. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Elle s'arrête. Elle n'arrive pas à la porte. Les cubes sont encore sur le tapis. Une autre voiture bleue attend. Elle non plus ne peut pas passer. Le pain veut aller au bout du couloir. Je voulais le livrer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux. Maman dit : le jeu est fini. On va &lt;emphasis level="moderate"&gt;ranger&lt;/emphasis&gt;. Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine. Maman dit : merci. Plus tard, Kenzo joue aux voitures dans le couloir. Les roues font un bruit léger. Maman dit : on range. Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui. Il craque. Le couloir est un peu frais. Le tapis du salon est épais. Amir est à genoux au milieu. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui. Avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Les voitures vont chercher le pain. Jusqu'au bout du couloir. Oui. On le mange là-bas. Papa pose un petit morceau de pain près de la porte. Il est encore tiède. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Elle s'arrête. Elle n'arrive pas à la porte. Les cubes sont encore sur le tapis. Une autre voiture bleue attend. Elle non plus ne peut pas passer. Le pain veut aller au bout du couloir. Je voulais le livrer.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,55 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dans la maison, l'horloge fait tic-tac.
-narrateur|Une odeur de pain chaud vient de la cuisine.
-narrateur|Le couloir est long, un peu frais.
-narrateur|Le tapis du salon est épais et doux.
-papa|Le pain est sorti, maman.
-maman|Merci, papa. Il sent bon.
-narrateur|Et maintenant, Amir est au salon.
-narrateur|Des cubes attendent dans une caisse en bois.
-narrateur|Amir les sort, un par un.
-narrateur|Les cubes font un bruit sec.
-enfant-m|Je fais une maison, maman.
-maman|Une maison en cubes. Elle est solide ?
-enfant-m|Oui. Elle est solide.
+          <t>narrateur|Au loin, une clochette de vélo.
+narrateur|Ting.
+narrateur|Papa a de la farine sur le tablier.
+narrateur|Une baguette craque quand il la casse.
+narrateur|L'odeur du pain chaud remplit la maison.
+maman|Il est encore tout chaud.
+papa|Oui. Il craque.
+narrateur|Le couloir est un peu frais.
+narrateur|Le tapis du salon est épais.
+narrateur|Amir est à genoux au milieu.
+narrateur|Des cubes rouges et bleus attendent.
+enfant-m|Je fais la boulangerie, maman.
+maman|Une maison pour le pain ?
+enfant-m|Oui. Avec une porte.
 narrateur|Amir pose un cube rouge.
 narrateur|Puis un cube bleu.
-narrateur|La maison grandit au milieu du tapis.
+narrateur|La maison grandit.
+narrateur|Les cubes font un bruit sec.
 papa|Ta maison a une porte ?
 enfant-m|Une petite porte, papa.
-narrateur|Puis le jeu est fini.
-maman|Le jeu est fini, Amir.
-maman|On va ranger.
-maman|Les jouets retournent dans la caisse.
-narrateur|Amir prend les cubes, un par un.
-narrateur|Il les met dans la caisse.
-narrateur|Toc. Toc. Toc.
-maman|Bravo. Ranger, c'est mettre dans la caisse.
-narrateur|La caisse se remplit.
-narrateur|Le tapis redevient vide.
-papa|Tu as fini de ranger tes jouets ?
-enfant-m|Oui, papa. Les cubes sont dans la caisse.
-maman|Merci, Amir. Tu as fait du bon travail.
-narrateur|Plus tard, le couloir est calme.
-narrateur|Amir sort de petites voitures.
+narrateur|Amir laisse un trou.
+narrateur|C'est la porte de la boulangerie.
+enfant-m|Les voitures vont chercher le pain.
+papa|Jusqu'au bout du couloir.
+enfant-m|Oui. On le mange là-bas.
+narrateur|Papa pose un petit morceau de pain près de la porte.
+narrateur|Il est encore tiède.
+narrateur|Amir prend une petite voiture rouge.
 narrateur|Les roues font un bruit léger.
-enfant-m|Elles vont jusqu'à la porte.
-papa|Elles roulent bien.
-narrateur|Puis ce jeu se termine aussi.
-maman|On range.
-narrateur|Amir se souvient.
-narrateur|Il prend les voitures.
-narrateur|Il les met dans la caisse.
-enfant-m|Dans la caisse, comme les cubes.
-maman|Oui. Même leçon, autre lieu.
-papa|Parce que tu ranges, le couloir est libre.
-narrateur|Amir a rangé deux fois.
-maman|Bravo, Amir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|La voiture avance.
+narrateur|Elle bute contre un cube.
+narrateur|Elle s'arrête.
+enfant-m|Elle n'arrive pas à la porte.
+maman|Les cubes sont encore sur le tapis.
+narrateur|Une autre voiture bleue attend.
+narrateur|Elle non plus ne peut pas passer.
+papa|Le pain veut aller au bout du couloir.
+enfant-m|Je voulais le livrer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1393,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le jeu est fini. Que fait Kenzo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le jeu est fini. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1432,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les jouets dans la caisse. Que fait Kenzo ?</t>
+          <t>Il met les jouets dans la caisse. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1556,7 +1547,6 @@
           <t>narrateur|Le jeu est fini. Que fait Amir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1581,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a rangé les cubes. Puis les voitures. Dans la caisse, deux fois. Tu t'es souvenu, Amir. Les jouets vont dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Le salon est calme. Le couloir est libre. Tu as fini de ranger tes jouets ? Oui. Deux fois. C'est du bon travail.</t>
+          <t>Amir prend les cubes, un par un. Il les met dans la caisse en bois. Toc. Toc. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Pour la route. Le tapis redevient libre. La voiture rouge avance. Elle passe la porte. Amir pose le petit pain sur le toit. Doucement. Il est encore chaud. La voiture bleue suit. Elles roulent dans le couloir. Livraison ! Au bout du couloir, les voitures s'arrêtent. Amir veut s'asseoir pour goûter. Les voitures sont sous ses genoux. Encore un peu de place ? Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Deux fois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo a rangé les cubes. Puis les voitures. Dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;, deux fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir prend les cubes, un par un. Il les met dans la caisse en bois. Toc. Toc. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Pour la route. Le tapis redevient libre. La voiture rouge avance. Elle passe la porte. Amir pose le petit pain sur le toit. Doucement. Il est encore chaud. La voiture bleue suit. Elles roulent dans le couloir. Livraison ! Au bout du couloir, les voitures s'arrêtent. Amir veut s'asseoir pour goûter. Les voitures sont sous ses genoux. Encore un peu de place ? Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Deux fois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1725,20 +1715,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amir a rangé les cubes.
-narrateur|Puis les voitures.
-narrateur|Dans la caisse, deux fois.
-maman|Tu t'es souvenu, Amir.
-enfant-m|Les jouets vont dans la caisse.
-papa|Oui. Ranger, c'est mettre dans la caisse.
-maman|Le salon est calme.
-maman|Le couloir est libre.
-papa|Tu as fini de ranger tes jouets ?
-enfant-m|Oui. Deux fois.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir prend les cubes, un par un.
+narrateur|Il les met dans la caisse en bois.
+narrateur|Toc. Toc. Toc.
+maman|On va ranger.
+maman|Tu ranges les cubes.
+enfant-m|Dans la caisse. Pour la route.
+narrateur|Le tapis redevient libre.
+narrateur|La voiture rouge avance.
+narrateur|Elle passe la porte.
+narrateur|Amir pose le petit pain sur le toit.
+papa|Doucement. Il est encore chaud.
+narrateur|La voiture bleue suit.
+narrateur|Elles roulent dans le couloir.
+enfant-m|Livraison !
+narrateur|Au bout du couloir, les voitures s'arrêtent.
+narrateur|Amir veut s'asseoir pour goûter.
+narrateur|Les voitures sont sous ses genoux.
+maman|Encore un peu de place ?
+narrateur|Amir se souvient.
+narrateur|Il prend les voitures.
+narrateur|Il les met dans la caisse.
+enfant-m|Dans la caisse, comme les cubes.
+papa|Oui. Deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1763,12 +1764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La caisse est fermée. Ça fait toc. L'horloge fait encore tic-tac. Tu veux une petite tranche de pain ? Oui, papa. Papa lui tend un morceau encore un peu chaud. On s'assoit un moment ? Amir s'assoit près de maman. Le tapis est doux sous les pieds. La caisse est pleine. Oui. Merci, Amir. Bravo. Tu as fait du bon travail.</t>
+          <t>Le bout du couloir est libre. Papa tend le morceau de pain. Il est encore un peu chaud. Amir s'assoit par terre. On s'assoit avec toi. Ils goûtent. Il craque. Oui. La croûte. Un peu de farine est sur le nez de papa. Amir rit. La boulangerie a bien livré. Les voitures dorment. Dans la caisse. Au loin, la clochette de vélo encore. Ting.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt; est fermée. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bout du couloir est libre. Papa tend le morceau de pain. Il est encore un peu chaud. Amir s'assoit par terre. On s'assoit avec toi. Ils goûtent. Il craque. Oui. La croûte. Un peu de farine est sur le nez de papa. Amir rit. La boulangerie a bien livré. Les voitures dorment. Dans la caisse. Au loin, la clochette de vélo encore. Ting.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1903,21 +1904,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La caisse est fermée.
-narrateur|Ça fait toc.
-narrateur|L'horloge fait encore tic-tac.
-papa|Tu veux une petite tranche de pain ?
-enfant-m|Oui, papa.
-narrateur|Papa lui tend un morceau encore un peu chaud.
-maman|On s'assoit un moment ?
-narrateur|Amir s'assoit près de maman.
-narrateur|Le tapis est doux sous les pieds.
-enfant-m|La caisse est pleine.
-maman|Oui. Merci, Amir.
-papa|Bravo. Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le bout du couloir est libre.
+narrateur|Papa tend le morceau de pain.
+narrateur|Il est encore un peu chaud.
+narrateur|Amir s'assoit par terre.
+maman|On s'assoit avec toi.
+narrateur|Ils goûtent.
+enfant-m|Il craque.
+papa|Oui. La croûte.
+narrateur|Un peu de farine est sur le nez de papa.
+narrateur|Amir rit.
+maman|La boulangerie a bien livré.
+enfant-m|Les voitures dorment.
+papa|Dans la caisse.
+narrateur|Au loin, la clochette de vélo encore.
+narrateur|Ting.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1942,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai rangé deux fois, dans la caisse. Bravo. Les cubes et les voitures sont rentrés. L'odeur du pain reste un peu. L'histoire est finie.</t>
+          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2082,14 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai rangé deux fois, dans la caisse.
-maman|Bravo.
-papa|Les cubes et les voitures sont rentrés.
-narrateur|L'odeur du pain reste un peu.
+          <t>enfant-m|On a mangé le pain au bout du couloir.
+maman|Après la livraison.
+narrateur|Les cubes et les voitures sont dans la caisse.
+papa|La maison sent encore le pain.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2108,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain. L'histoire est finie.</t>
+          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain. L'histoire est finie.</t>
+          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2088,8 +2088,7 @@
           <t>enfant-m|On a mangé le pain au bout du couloir.
 maman|Après la livraison.
 narrateur|Les cubes et les voitures sont dans la caisse.
-papa|La maison sent encore le pain.
-narrateur|L'histoire est finie.</t>
+papa|La maison sent encore le pain.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2159,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon puis couloir</t>
+          <t>salon puis couloir, après la fournée</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon puis couloir, après la fournée</t>
+          <t>salon puis couloir, farine, clochette de vélo, après la fournée</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir veut livrer le pain chaud jusqu'au bout du couloir. Les cubes gênent les voitures. Il range deux fois. Ils goûtent.</t>
+          <t>Amir veut livrer le pain chaud au bout du couloir, avec son doudou. La maison de cubes tombe sur le doudou. Il cherche, met cubes puis voitures dans la caisse. Le doudou apparaît sous les voitures. Ils goûtent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui. Il craque. Le couloir est un peu frais. Le tapis du salon est épais. Amir est à genoux au milieu. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui. Avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Les voitures vont chercher le pain. Jusqu'au bout du couloir. Oui. On le mange là-bas. Papa pose un petit morceau de pain près de la porte. Il est encore tiède. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Elle s'arrête. Elle n'arrive pas à la porte. Les cubes sont encore sur le tapis. Une autre voiture bleue attend. Elle non plus ne peut pas passer. Le pain veut aller au bout du couloir. Je voulais le livrer.</t>
+          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui, il craque. Le couloir est un peu frais. Le tapis du salon est épais. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Jusqu'au bout du couloir ? Oui, on le mange là-bas. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. La maison a bougé. Amir cherche le tissu beige. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou. Seulement le pain tiède. Sous la table ? Il se penche. L'ombre est vide. Il est perdu. Les cubes sont encore tout autour. Je veux voir dessous. Amir prend un cube rouge. Il le pose dans la caisse en bois. Toc. Le bois sent un peu la forêt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui. Il craque. Le couloir est un peu frais. Le tapis du salon est épais. Amir est à genoux au milieu. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui. Avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Les voitures vont chercher le pain. Jusqu'au bout du couloir. Oui. On le mange là-bas. Papa pose un petit morceau de pain près de la porte. Il est encore tiède. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Elle s'arrête. Elle n'arrive pas à la porte. Les cubes sont encore sur le tapis. Une autre voiture bleue attend. Elle non plus ne peut pas passer. Le pain veut aller au bout du couloir. Je voulais le livrer.</t>
+          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui, il craque. Le couloir est un peu frais. Le tapis du salon est épais. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Jusqu'au bout du couloir ? Oui, on le mange là-bas. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. La maison a bougé. Amir cherche le tissu beige. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou. Seulement le pain tiède. Sous la table ? Il se penche. L'ombre est vide. Il est perdu. Les cubes sont encore tout autour. Je veux voir dessous. Amir prend un cube rouge. Il le pose dans la caisse en bois. Toc. Le bois sent un peu la forêt.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1330,38 +1330,51 @@
 narrateur|Une baguette craque quand il la casse.
 narrateur|L'odeur du pain chaud remplit la maison.
 maman|Il est encore tout chaud.
-papa|Oui. Il craque.
+papa|Oui, il craque.
 narrateur|Le couloir est un peu frais.
 narrateur|Le tapis du salon est épais.
-narrateur|Amir est à genoux au milieu.
+narrateur|En ce moment, Amir est à genoux.
 narrateur|Des cubes rouges et bleus attendent.
 enfant-m|Je fais la boulangerie, maman.
 maman|Une maison pour le pain ?
-enfant-m|Oui. Avec une porte.
+enfant-m|Oui, avec une porte.
 narrateur|Amir pose un cube rouge.
 narrateur|Puis un cube bleu.
-narrateur|La maison grandit.
+narrateur|La maison grandit au milieu du tapis.
 narrateur|Les cubes font un bruit sec.
 papa|Ta maison a une porte ?
 enfant-m|Une petite porte, papa.
 narrateur|Amir laisse un trou.
 narrateur|C'est la porte de la boulangerie.
-enfant-m|Les voitures vont chercher le pain.
-papa|Jusqu'au bout du couloir.
-enfant-m|Oui. On le mange là-bas.
-narrateur|Papa pose un petit morceau de pain près de la porte.
-narrateur|Il est encore tiède.
+narrateur|Le doudou beige est assis contre le mur.
+enfant-m|Toi, tu attends le pain.
+narrateur|Papa pose un morceau tiède près de la porte.
+enfant-m|Les voitures vont le livrer.
+papa|Jusqu'au bout du couloir ?
+enfant-m|Oui, on le mange là-bas.
 narrateur|Amir prend une petite voiture rouge.
 narrateur|Les roues font un bruit léger.
 narrateur|La voiture avance.
 narrateur|Elle bute contre un cube.
-narrateur|Elle s'arrête.
-enfant-m|Elle n'arrive pas à la porte.
-maman|Les cubes sont encore sur le tapis.
-narrateur|Une autre voiture bleue attend.
-narrateur|Elle non plus ne peut pas passer.
-papa|Le pain veut aller au bout du couloir.
-enfant-m|Je voulais le livrer.</t>
+narrateur|Un pan de la maison glisse.
+narrateur|Des cubes tombent sur le doudou.
+enfant-m|Oh.
+maman|La maison a bougé.
+narrateur|Amir cherche le tissu beige.
+enfant-m|Où est mon doudou ?
+papa|Derrière la porte de la boulangerie ?
+narrateur|Amir regarde le trou.
+narrateur|Seulement le pain tiède.
+enfant-m|Sous la table ?
+narrateur|Il se penche.
+narrateur|L'ombre est vide.
+enfant-m|Il est perdu.
+maman|Les cubes sont encore tout autour.
+enfant-m|Je veux voir dessous.
+narrateur|Amir prend un cube rouge.
+narrateur|Il le pose dans la caisse en bois.
+narrateur|Toc.
+narrateur|Le bois sent un peu la forêt.</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Amir ?</t>
+          <t>Amir cherche son doudou. Où est-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Amir ?</t>
+          <t>Amir cherche son doudou. Où est-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1403,12 +1416,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>le doudou</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | il range | la caisse | dans la caisse | mettre dans la caisse</t>
+          <t>le doudou | doudou | sous les voitures | sous les cubes | dessous | près de la porte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1423,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les jouets dans la caisse. Que fait Amir ?</t>
+          <t>Il cherche sous les cubes et les voitures. Où est le doudou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1465,14 +1478,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1544,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le jeu est fini. Que fait Amir ?</t>
+          <t>narrateur|Amir cherche son doudou.
+narrateur|Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir prend les cubes, un par un. Il les met dans la caisse en bois. Toc. Toc. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Pour la route. Le tapis redevient libre. La voiture rouge avance. Elle passe la porte. Amir pose le petit pain sur le toit. Doucement. Il est encore chaud. La voiture bleue suit. Elles roulent dans le couloir. Livraison ! Au bout du couloir, les voitures s'arrêtent. Amir veut s'asseoir pour goûter. Les voitures sont sous ses genoux. Encore un peu de place ? Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Deux fois.</t>
+          <t>Un cube bleu va dans la caisse. Toc. Amir écarte encore un mur. Tu regardes bien sous la maison ? Oui, maman. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Il sent encore le tapis du salon. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues. Le bout du couloir est libre, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Amir prend les cubes, un par un. Il les met dans la caisse en bois. Toc. Toc. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Pour la route. Le tapis redevient libre. La voiture rouge avance. Elle passe la porte. Amir pose le petit pain sur le toit. Doucement. Il est encore chaud. La voiture bleue suit. Elles roulent dans le couloir. Livraison ! Au bout du couloir, les voitures s'arrêtent. Amir veut s'asseoir pour goûter. Les voitures sont sous ses genoux. Encore un peu de place ? Amir se souvient. Il prend les voitures. Il les met dans la caisse. Dans la caisse, comme les cubes. Oui. Deux fois.</t>
+          <t>Un cube bleu va dans la caisse. Toc. Amir écarte encore un mur. Tu regardes bien sous la maison ? Oui, maman. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Il sent encore le tapis du salon. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues. Le bout du couloir est libre, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1639,7 +1653,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1715,29 +1729,34 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amir prend les cubes, un par un.
-narrateur|Il les met dans la caisse en bois.
-narrateur|Toc. Toc. Toc.
-maman|On va ranger.
-maman|Tu ranges les cubes.
-enfant-m|Dans la caisse. Pour la route.
-narrateur|Le tapis redevient libre.
-narrateur|La voiture rouge avance.
-narrateur|Elle passe la porte.
-narrateur|Amir pose le petit pain sur le toit.
-papa|Doucement. Il est encore chaud.
-narrateur|La voiture bleue suit.
-narrateur|Elles roulent dans le couloir.
-enfant-m|Livraison !
-narrateur|Au bout du couloir, les voitures s'arrêtent.
-narrateur|Amir veut s'asseoir pour goûter.
-narrateur|Les voitures sont sous ses genoux.
-maman|Encore un peu de place ?
-narrateur|Amir se souvient.
-narrateur|Il prend les voitures.
-narrateur|Il les met dans la caisse.
-enfant-m|Dans la caisse, comme les cubes.
-papa|Oui. Deux fois.</t>
+          <t>narrateur|Un cube bleu va dans la caisse.
+narrateur|Toc.
+narrateur|Amir écarte encore un mur.
+maman|Tu regardes bien sous la maison ?
+enfant-m|Oui, maman.
+narrateur|Le tapis reparaît, un peu.
+narrateur|Pas de tissu beige.
+papa|Peut-être plus loin, vers le couloir.
+narrateur|Amir prend le morceau de pain.
+narrateur|Il le pose sur la voiture rouge.
+enfant-m|On va au bout.
+narrateur|Le couloir est un peu frais.
+narrateur|D'autres petites voitures attendent.
+narrateur|Une voiture bleue barre le chemin.
+narrateur|Une jaune aussi.
+enfant-m|Elles cachent le sol.
+narrateur|Amir glisse la bleue dans la caisse.
+narrateur|Toc.
+narrateur|Puis la jaune.
+narrateur|Un bout de tissu dépasse près de la porte.
+enfant-m|Mon doudou !
+narrateur|Le doudou était sous les voitures.
+narrateur|Il sent encore le tapis du salon.
+narrateur|Amir le serre contre sa joue.
+papa|Merci, tu l'as trouvé.
+maman|Te voilà, petit.
+enfant-m|Il était sous les roues.
+narrateur|Le bout du couloir est libre, maintenant.</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le bout du couloir est libre. Papa tend le morceau de pain. Il est encore un peu chaud. Amir s'assoit par terre. On s'assoit avec toi. Ils goûtent. Il craque. Oui. La croûte. Un peu de farine est sur le nez de papa. Amir rit. La boulangerie a bien livré. Les voitures dorment. Dans la caisse. Au loin, la clochette de vélo encore. Ting.</t>
+          <t>L'horloge fait tic-tac, tout doux. Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de pain. La croûte craque encore. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Le bout du couloir est libre. Papa tend le morceau de pain. Il est encore un peu chaud. Amir s'assoit par terre. On s'assoit avec toi. Ils goûtent. Il craque. Oui. La croûte. Un peu de farine est sur le nez de papa. Amir rit. La boulangerie a bien livré. Les voitures dorment. Dans la caisse. Au loin, la clochette de vélo encore. Ting.</t>
+          <t>L'horloge fait tic-tac, tout doux. Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de pain. La croûte craque encore. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1832,7 +1851,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1904,21 +1923,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le bout du couloir est libre.
-narrateur|Papa tend le morceau de pain.
-narrateur|Il est encore un peu chaud.
-narrateur|Amir s'assoit par terre.
-maman|On s'assoit avec toi.
-narrateur|Ils goûtent.
-enfant-m|Il craque.
-papa|Oui. La croûte.
-narrateur|Un peu de farine est sur le nez de papa.
-narrateur|Amir rit.
-maman|La boulangerie a bien livré.
-enfant-m|Les voitures dorment.
-papa|Dans la caisse.
-narrateur|Au loin, la clochette de vélo encore.
-narrateur|Ting.</t>
+          <t>narrateur|L'horloge fait tic-tac, tout doux.
+narrateur|Amir s'assoit au bout du couloir.
+narrateur|Le doudou est sur ses genoux.
+narrateur|Papa lui tend le morceau de pain.
+narrateur|La croûte craque encore.
+enfant-m|Il est chaud.
+maman|On le mange ici, comme prévu.
+papa|Tu veux une petite miette pour lui ?
+enfant-m|Une toute petite.
+narrateur|Amir pose une miette sur le tissu.
+narrateur|Le doudou reste bien droit.
+narrateur|L'odeur du pain remplit le couloir.
+maman|On est bien, ici.
+enfant-m|La voiture a fini la course.
+papa|Oui, jusqu'au bout.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain.</t>
+          <t>Le doudou a du pain. Toi aussi. Bravo, tu l'as retrouvé. La farine reste un peu sur le tablier. Le couloir sent encore la croûte chaude.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le pain au bout du couloir. Après la livraison. Les cubes et les voitures sont dans la caisse. La maison sent encore le pain.</t>
+          <t>Le doudou a du pain. Toi aussi. Bravo, tu l'as retrouvé. La farine reste un peu sur le tablier. Le couloir sent encore la croûte chaude.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2013,7 +2032,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2085,10 +2104,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a mangé le pain au bout du couloir.
-maman|Après la livraison.
-narrateur|Les cubes et les voitures sont dans la caisse.
-papa|La maison sent encore le pain.</t>
+          <t>enfant-m|Le doudou a du pain.
+maman|Toi aussi.
+papa|Bravo, tu l'as retrouvé.
+narrateur|La farine reste un peu sur le tablier.
+narrateur|Le couloir sent encore la croûte chaude.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2186,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-03.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir veut livrer le pain chaud au bout du couloir, avec son doudou. La maison de cubes tombe sur le doudou. Il cherche, met cubes puis voitures dans la caisse. Le doudou apparaît sous les voitures. Ils goûtent.</t>
+          <t>Une clochette de vélo traverse la rue. Ting. Sur la planche, un éclat de farine brille. Amir veut livrer le pain tiède au bout du couloir, maintenant. La maison de cubes tombe sur le doudou. Il cherche d'un coup : trou, table, tout écarter. Rien. Il refuse de foncer, met les cubes dans la caisse. Les voitures barrent le couloir. Il retrouve l'éclat près des roues. Le doudou apparaît. Sur la croûte, l'éclat garde une trace blanche.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui, il craque. Le couloir est un peu frais. Le tapis du salon est épais. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Jusqu'au bout du couloir ? Oui, on le mange là-bas. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. La maison a bougé. Amir cherche le tissu beige. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou. Seulement le pain tiède. Sous la table ? Il se penche. L'ombre est vide. Il est perdu. Les cubes sont encore tout autour. Je veux voir dessous. Amir prend un cube rouge. Il le pose dans la caisse en bois. Toc. Le bois sent un peu la forêt.</t>
+          <t>Une clochette de vélo traverse la rue, nette. Ting. Dans la maison, l'odeur de croûte répond. Papa a de la farine sur le tablier. Sur la planche, un éclat de farine brille. Il est blanc, papa. C'est un reste de la fournée. L'éclat de farine tient comme une petite lune. Le tapis du salon est épais, chaud. Le couloir, plus loin, reste un peu frais. Le pain est tiède, Amir. Je le veux au bout, maintenant. Au bout du couloir ? Oui, on le mange là-bas. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent sur le tapis. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une petite porte. Amir pose un cube rouge, puis un bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou, bien net. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Amir prend une petite voiture rouge. Les roues font un bruit léger sur le tapis. La voiture avance trop vite. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La maison a bougé. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou, d'un coup. Seulement le pain tiède. Sous la table ? Il se penche, trop vite. L'ombre est vide. Il est perdu. Amir veut tout écarter d'un seul geste. Les cubes glissent plus loin, plus nombreux. Ça ne veut pas. Ses épaules tombent un peu. Ça serre, dans son ventre. Maman se baisse à sa hauteur. Tu regardes sous les cubes ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Au loin, une clochette de vélo. Ting. Papa a de la farine sur le tablier. Une baguette craque quand il la casse. L'odeur du pain chaud remplit la maison. Il est encore tout chaud. Oui, il craque. Le couloir est un peu frais. Le tapis du salon est épais. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une porte. Amir pose un cube rouge. Puis un cube bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Jusqu'au bout du couloir ? Oui, on le mange là-bas. Amir prend une petite voiture rouge. Les roues font un bruit léger. La voiture avance. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. La maison a bougé. Amir cherche le tissu beige. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou. Seulement le pain tiède. Sous la table ? Il se penche. L'ombre est vide. Il est perdu. Les cubes sont encore tout autour. Je veux voir dessous. Amir prend un cube rouge. Il le pose dans la caisse en bois. Toc. Le bois sent un peu la forêt.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une clochette de vélo traverse la rue, nette. Ting. Dans la maison, l'odeur de croûte répond. Papa a de la farine sur le tablier. Sur la planche, un &lt;emphasis level="moderate"&gt;éclat de farine&lt;/emphasis&gt; brille. Il est blanc, papa. C'est un reste de la fournée. L'éclat de farine tient comme une petite lune. Le tapis du salon est épais, chaud. Le couloir, plus loin, reste un peu frais. Le pain est tiède, Amir. Je le veux au bout, maintenant. Au bout du couloir ? Oui, on le mange là-bas. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent sur le tapis. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une petite porte. Amir pose un cube rouge, puis un bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou, bien net. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Amir prend une petite voiture rouge. Les roues font un bruit léger sur le tapis. La voiture avance trop vite. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La maison a bougé. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou, d'un coup. Seulement le pain tiède. Sous la table ? Il se penche, trop vite. L'ombre est vide. Il est perdu. Amir veut tout écarter d'un seul geste. Les cubes glissent plus loin, plus nombreux. Ça ne veut pas. Ses épaules tombent un peu. Ça serre, dans son ventre. Maman se baisse à sa hauteur. Tu regardes sous les cubes ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo joue aux cubes dans le salon. Les cubes font un bruit sec. Le tapis est doux. Maman dit : le jeu est fini. On va &lt;emphasis&gt;ranger&lt;/emphasis&gt;. Les jouets retournent dans la caisse. Kenzo prend les cubes, un par un. Il les met dans la caisse. La caisse est pleine. Maman dit : merci. Plus tard, Kenzo joue aux voitures dans le couloir. Les roues font un bruit léger. Maman dit : on range. Kenzo se souvient. Il prend les voitures. Il les met dans la caisse. Ranger, c'est mettre dans la caisse. Même leçon, autre lieu. Kenzo a rangé deux fois. [pause]</t>
+          <t>Une clochette de vélo traverse la rue, nette. Ting. Dans la maison, l'odeur de croûte répond. Papa a de la farine sur le tablier. Sur la planche, un &lt;emphasis&gt;éclat de farine&lt;/emphasis&gt; brille. Il est blanc, papa. C'est un reste de la fournée. L'éclat de farine tient comme une petite lune. Le tapis du salon est épais, chaud. Le couloir, plus loin, reste un peu frais. Le pain est tiède, Amir. Je le veux au bout, maintenant. Au bout du couloir ? Oui, on le mange là-bas. En ce moment, Amir est à genoux. Des cubes rouges et bleus attendent sur le tapis. Je fais la boulangerie, maman. Une maison pour le pain ? Oui, avec une petite porte. Amir pose un cube rouge, puis un bleu. La maison grandit au milieu du tapis. Les cubes font un bruit sec. Ta maison a une porte ? Une petite porte, papa. Amir laisse un trou, bien net. C'est la porte de la boulangerie. Le doudou beige est assis contre le mur. Toi, tu attends le pain. Papa pose un morceau tiède près de la porte. Les voitures vont le livrer. Amir prend une petite voiture rouge. Les roues font un bruit léger sur le tapis. La voiture avance trop vite. Elle bute contre un cube. Un pan de la maison glisse. Des cubes tombent sur le doudou. Oh. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La maison a bougé. Où est mon doudou ? Derrière la porte de la boulangerie ? Amir regarde le trou, d'un coup. Seulement le pain tiède. Sous la table ? Il se penche, trop vite. L'ombre est vide. Il est perdu. Amir veut tout écarter d'un seul geste. Les cubes glissent plus loin, plus nombreux. Ça ne veut pas. Ses épaules tombent un peu. Ça serre, dans son ventre. Maman se baisse à sa hauteur. Tu regardes sous les cubes ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>éclat de farine</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,60 +1321,73 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_le_pain_au_bout_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Au loin, une clochette de vélo.
+          <t>narrateur|Une clochette de vélo traverse la rue, nette.
 narrateur|Ting.
+narrateur|Dans la maison, l'odeur de croûte répond.
 narrateur|Papa a de la farine sur le tablier.
-narrateur|Une baguette craque quand il la casse.
-narrateur|L'odeur du pain chaud remplit la maison.
-maman|Il est encore tout chaud.
-papa|Oui, il craque.
-narrateur|Le couloir est un peu frais.
-narrateur|Le tapis du salon est épais.
+narrateur|Sur la planche, un éclat de farine brille.
+enfant-m|Il est blanc, papa.
+papa|C'est un reste de la fournée.
+narrateur|L'éclat de farine tient comme une petite lune.
+narrateur|Le tapis du salon est épais, chaud.
+narrateur|Le couloir, plus loin, reste un peu frais.
+maman|Le pain est tiède, Amir.
+enfant-m|Je le veux au bout, maintenant.
+papa|Au bout du couloir ?
+enfant-m|Oui, on le mange là-bas.
 narrateur|En ce moment, Amir est à genoux.
-narrateur|Des cubes rouges et bleus attendent.
+narrateur|Des cubes rouges et bleus attendent sur le tapis.
 enfant-m|Je fais la boulangerie, maman.
 maman|Une maison pour le pain ?
-enfant-m|Oui, avec une porte.
-narrateur|Amir pose un cube rouge.
-narrateur|Puis un cube bleu.
+enfant-m|Oui, avec une petite porte.
+narrateur|Amir pose un cube rouge, puis un bleu.
 narrateur|La maison grandit au milieu du tapis.
 narrateur|Les cubes font un bruit sec.
 papa|Ta maison a une porte ?
 enfant-m|Une petite porte, papa.
-narrateur|Amir laisse un trou.
+narrateur|Amir laisse un trou, bien net.
 narrateur|C'est la porte de la boulangerie.
 narrateur|Le doudou beige est assis contre le mur.
 enfant-m|Toi, tu attends le pain.
 narrateur|Papa pose un morceau tiède près de la porte.
 enfant-m|Les voitures vont le livrer.
-papa|Jusqu'au bout du couloir ?
-enfant-m|Oui, on le mange là-bas.
 narrateur|Amir prend une petite voiture rouge.
-narrateur|Les roues font un bruit léger.
-narrateur|La voiture avance.
+narrateur|Les roues font un bruit léger sur le tapis.
+narrateur|La voiture avance trop vite.
 narrateur|Elle bute contre un cube.
 narrateur|Un pan de la maison glisse.
 narrateur|Des cubes tombent sur le doudou.
 enfant-m|Oh.
+narrateur|Le sourire d'Amir disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
 maman|La maison a bougé.
-narrateur|Amir cherche le tissu beige.
 enfant-m|Où est mon doudou ?
 papa|Derrière la porte de la boulangerie ?
-narrateur|Amir regarde le trou.
+narrateur|Amir regarde le trou, d'un coup.
 narrateur|Seulement le pain tiède.
 enfant-m|Sous la table ?
-narrateur|Il se penche.
+narrateur|Il se penche, trop vite.
 narrateur|L'ombre est vide.
 enfant-m|Il est perdu.
-maman|Les cubes sont encore tout autour.
-enfant-m|Je veux voir dessous.
-narrateur|Amir prend un cube rouge.
-narrateur|Il le pose dans la caisse en bois.
-narrateur|Toc.
-narrateur|Le bois sent un peu la forêt.</t>
+narrateur|Amir veut tout écarter d'un seul geste.
+narrateur|Les cubes glissent plus loin, plus nombreux.
+enfant-m|Ça ne veut pas.
+narrateur|Ses épaules tombent un peu.
+narrateur|Ça serre, dans son ventre.
+narrateur|Maman se baisse à sa hauteur.
+maman|Tu regardes sous les cubes ?</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>clochette,cubes,voiture</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1419,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Amir cherche son doudou. Où est-il ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amir cherche son &lt;emphasis level="moderate"&gt;doudou&lt;/emphasis&gt;. Où est-il ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Kenzo ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Amir cherche son &lt;emphasis&gt;doudou&lt;/emphasis&gt;. Où est-il ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1474,7 +1487,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1482,10 +1495,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,34 +1513,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1536,23 +1553,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=le_doudou_est_sous_le_bazar; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1585,17 +1602,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Un cube bleu va dans la caisse. Toc. Amir écarte encore un mur. Tu regardes bien sous la maison ? Oui, maman. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Il sent encore le tapis du salon. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues. Le bout du couloir est libre, maintenant.</t>
+          <t>Amir refuse d'écarter tout d'un coup. Il pose un genou sur le tapis. Un cube rouge va dans la caisse. Toc. Le bois sent un peu la forêt. Je le mets, maman. Tu regardes bien sous la maison ? Oui, maman. Un cube bleu rejoint le rouge. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir veut les pousser d'un coup. Puis il s'arrête. Attends, je regarde. Amir refuse de foncer. Il écoute le couloir, un instant. Sur le tapis, un éclat de farine brille. Comme sur la planche ! Tu le vois, toi ? Oui, près des roues. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Un éclat de farine tient sur son oreille. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Un cube bleu va dans la caisse. Toc. Amir écarte encore un mur. Tu regardes bien sous la maison ? Oui, maman. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Il sent encore le tapis du salon. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues. Le bout du couloir est libre, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir refuse d'écarter tout d'un coup. Il pose un genou sur le tapis. Un cube rouge va dans la caisse. Toc. Le bois sent un peu la forêt. Je le mets, maman. Tu regardes bien sous la maison ? Oui, maman. Un cube bleu rejoint le rouge. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir veut les pousser d'un coup. Puis il s'arrête. Attends, je regarde. Amir refuse de foncer. Il écoute le couloir, un instant. Sur le tapis, un &lt;emphasis level="moderate"&gt;éclat de farine&lt;/emphasis&gt; brille. Comme sur la planche ! Tu le vois, toi ? Oui, près des roues. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Un éclat de farine tient sur son oreille. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a rangé les cubes. Puis les voitures. Dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;, deux fois. [pause]</t>
+          <t>Amir refuse d'écarter tout d'un coup. Il pose un genou sur le tapis. Un cube rouge va dans la caisse. Toc. Le bois sent un peu la forêt. Je le mets, maman. Tu regardes bien sous la maison ? Oui, maman. Un cube bleu rejoint le rouge. Le tapis reparaît, un peu. Pas de tissu beige. Peut-être plus loin, vers le couloir. Amir prend le morceau de pain. Il le pose sur la voiture rouge. On va au bout. Le couloir est un peu frais. D'autres petites voitures attendent. Une voiture bleue barre le chemin. Une jaune aussi. Elles cachent le sol. Amir veut les pousser d'un coup. Puis il s'arrête. Attends, je regarde. Amir refuse de foncer. Il écoute le couloir, un instant. Sur le tapis, un &lt;emphasis&gt;éclat de farine&lt;/emphasis&gt; brille. Comme sur la planche ! Tu le vois, toi ? Oui, près des roues. Amir glisse la bleue dans la caisse. Toc. Puis la jaune. Un bout de tissu dépasse près de la porte. Mon doudou ! Le doudou était sous les voitures. Un éclat de farine tient sur son oreille. Amir le serre contre sa joue. Merci, tu l'as trouvé. Te voilà, petit. Il était sous les roues. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1642,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1650,10 +1667,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,30 +1693,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>éclat de farine</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1708,10 +1725,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1724,16 +1741,20 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Un cube bleu va dans la caisse.
+          <t>narrateur|Amir refuse d'écarter tout d'un coup.
+narrateur|Il pose un genou sur le tapis.
+narrateur|Un cube rouge va dans la caisse.
 narrateur|Toc.
-narrateur|Amir écarte encore un mur.
+narrateur|Le bois sent un peu la forêt.
+enfant-m|Je le mets, maman.
 maman|Tu regardes bien sous la maison ?
 enfant-m|Oui, maman.
+narrateur|Un cube bleu rejoint le rouge.
 narrateur|Le tapis reparaît, un peu.
 narrateur|Pas de tissu beige.
 papa|Peut-être plus loin, vers le couloir.
@@ -1745,18 +1766,31 @@
 narrateur|Une voiture bleue barre le chemin.
 narrateur|Une jaune aussi.
 enfant-m|Elles cachent le sol.
+narrateur|Amir veut les pousser d'un coup.
+narrateur|Puis il s'arrête.
+enfant-m|Attends, je regarde.
+narrateur|Amir refuse de foncer.
+narrateur|Il écoute le couloir, un instant.
+narrateur|Sur le tapis, un éclat de farine brille.
+enfant-m|Comme sur la planche !
+papa|Tu le vois, toi ?
+enfant-m|Oui, près des roues.
 narrateur|Amir glisse la bleue dans la caisse.
 narrateur|Toc.
 narrateur|Puis la jaune.
 narrateur|Un bout de tissu dépasse près de la porte.
 enfant-m|Mon doudou !
 narrateur|Le doudou était sous les voitures.
-narrateur|Il sent encore le tapis du salon.
+narrateur|Un éclat de farine tient sur son oreille.
 narrateur|Amir le serre contre sa joue.
 papa|Merci, tu l'as trouvé.
 maman|Te voilà, petit.
-enfant-m|Il était sous les roues.
-narrateur|Le bout du couloir est libre, maintenant.</t>
+enfant-m|Il était sous les roues.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>caisse,voitures</t>
         </is>
       </c>
     </row>
@@ -1783,17 +1817,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>L'horloge fait tic-tac, tout doux. Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de pain. La croûte craque encore. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout.</t>
+          <t>Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de pain. La croûte craque sous les dents. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout. Sur la croûte, un éclat de farine brille. Comme sur la planche, papa. Au loin, la clochette de vélo reprend. Ting.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>L'horloge fait tic-tac, tout doux. Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de pain. La croûte craque encore. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de &lt;emphasis level="moderate"&gt;pain&lt;/emphasis&gt;. La croûte craque sous les dents. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout. Sur la croûte, un éclat de farine brille. Comme sur la planche, papa. Au loin, la clochette de vélo reprend. Ting.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;caisse&lt;/emphasis&gt; est fermée. Maman sourit. [pause]</t>
+          <t>Amir s'assoit au bout du couloir. Le doudou est sur ses genoux. Papa lui tend le morceau de &lt;emphasis&gt;pain&lt;/emphasis&gt;. La croûte craque sous les dents. Il est chaud. On le mange ici, comme prévu. Tu veux une petite miette pour lui ? Une toute petite. Amir pose une miette sur le tissu. Le doudou reste bien droit. L'odeur du pain remplit le couloir. On est bien, ici. La voiture a fini la course. Oui, jusqu'au bout. Sur la croûte, un éclat de farine brille. Comme sur la planche, papa. Au loin, la clochette de vélo reprend. Ting. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1840,7 +1874,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1882,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1874,30 +1908,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1906,10 +1940,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1920,14 +1954,17 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=refermer_le_désir; emotion=fierté_calme et chaleur; intensite=2; destinataire=enfant; sous_texte=le_pain_arrive_au_bout; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|L'horloge fait tic-tac, tout doux.
-narrateur|Amir s'assoit au bout du couloir.
+          <t>narrateur|Amir s'assoit au bout du couloir.
 narrateur|Le doudou est sur ses genoux.
 narrateur|Papa lui tend le morceau de pain.
-narrateur|La croûte craque encore.
+narrateur|La croûte craque sous les dents.
 enfant-m|Il est chaud.
 maman|On le mange ici, comme prévu.
 papa|Tu veux une petite miette pour lui ?
@@ -1937,7 +1974,16 @@
 narrateur|L'odeur du pain remplit le couloir.
 maman|On est bien, ici.
 enfant-m|La voiture a fini la course.
-papa|Oui, jusqu'au bout.</t>
+papa|Oui, jusqu'au bout.
+narrateur|Sur la croûte, un éclat de farine brille.
+enfant-m|Comme sur la planche, papa.
+narrateur|Au loin, la clochette de vélo reprend.
+narrateur|Ting.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pain,couloir</t>
         </is>
       </c>
     </row>
@@ -1964,17 +2010,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a du pain. Toi aussi. Bravo, tu l'as retrouvé. La farine reste un peu sur le tablier. Le couloir sent encore la croûte chaude.</t>
+          <t>Le doudou a du pain. Toi aussi. La farine reste un peu sur le tablier. Le couloir sent la croûte chaude. La chaleur touche les joues d'Amir. Sur le pain, l'éclat de farine garde une trace blanche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a du pain. Toi aussi. Bravo, tu l'as retrouvé. La farine reste un peu sur le tablier. Le couloir sent encore la croûte chaude.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a du pain. Toi aussi. La farine reste un peu sur le tablier. Le couloir sent la croûte chaude. La chaleur touche les joues d'Amir. Sur le pain, l'&lt;emphasis level="moderate"&gt;éclat de farine&lt;/emphasis&gt; garde une trace blanche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a du pain. Toi aussi. La farine reste un peu sur le tablier. Le couloir sent la croûte chaude. La chaleur touche les joues d'Amir. Sur le pain, l'&lt;emphasis&gt;éclat de farine&lt;/emphasis&gt; garde une trace blanche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2021,18 +2067,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2041,12 +2087,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2055,17 +2101,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de farine</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2074,11 +2124,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2087,28 +2137,38 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_de_la_planche_est_sur_la_croute; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>enfant-m|Le doudou a du pain.
 maman|Toi aussi.
-papa|Bravo, tu l'as retrouvé.
 narrateur|La farine reste un peu sur le tablier.
-narrateur|Le couloir sent encore la croûte chaude.</t>
+narrateur|Le couloir sent la croûte chaude.
+narrateur|La chaleur touche les joues d'Amir.
+narrateur|Sur le pain, l'éclat de farine garde une trace blanche.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>farine,pain</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2193,6 +2253,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
